--- a/campus-placement/qa/C-6-PDF-Report-Availability-and-Correctness.xlsx
+++ b/campus-placement/qa/C-6-PDF-Report-Availability-and-Correctness.xlsx
@@ -564,15 +564,11 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -631,15 +627,11 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="M3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -698,15 +690,11 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="M4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -765,15 +753,11 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="M5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -832,15 +816,11 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="M6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -899,15 +879,11 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="M7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -966,15 +942,11 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="M8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1033,15 +1005,11 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="M9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1100,15 +1068,11 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="M10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1167,15 +1131,11 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="M11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1234,15 +1194,11 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="M12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1301,15 +1257,11 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="M13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1368,15 +1320,11 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="M14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1435,15 +1383,11 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="M15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1502,15 +1446,11 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="M16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1569,15 +1509,11 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="M17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1636,15 +1572,11 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="M18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
